--- a/uploads/voucher_receiving_RK-202608-0001.xlsx
+++ b/uploads/voucher_receiving_RK-202608-0001.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入库验收单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入库单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,29 +28,24 @@
     <font>
       <name val="宋体"/>
       <b val="1"/>
-      <sz val="16"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -63,31 +58,43 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,160 +460,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>入库验收单</t>
-        </is>
-      </c>
+          <t>河曲县正成洗选煤有限责任公司入库单</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日期：</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>票号：</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>RK-202608-0001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>供应商：</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>单号</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>RK-202608-0001</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>订单号</t>
+          <t>仓库：</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>主库房</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>品种数：</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+          <t>品名</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>不含税单价</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>税率</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>不含税金额</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>含税金额</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>物资</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>测试品</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>货到付款: 下单后自动进入入库板块(整批1项)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>1.0个</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>合格数/不合格数</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>1.0 / 0</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>验收人</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>合计: 人民币大写：零元整</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>库管员签字：____________    验收员签字：____________    采购员：____________</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:29</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>货到付款: 下单后自动进入入库板块(整批1项)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>经手人：                验收人：                审批人：</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>第1页/共1页</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="F2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>